--- a/outputs/reports/enzyme_report.xlsx
+++ b/outputs/reports/enzyme_report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Enzymy" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Enzymy'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Enzymy'!$A$1:$P$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID UniProt</t>
+          <t>UniProt ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -463,34 +463,79 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Numer EC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Długość sekwencji</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Masa [Da]</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Numer EC</t>
+          <t>Masa cząsteczkowa</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Sekwencja aminokwasowa</t>
+          <t>Status rekordu</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status QC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Grupa duplikatów</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Czy reprezentant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aminokwasy hydrofobowe [%]</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Liczba cystein</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cysteiny [%]</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Najczęstszy aminokwas</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Interpretacja</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Sekwencja</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P00918</t>
+          <t>P04040</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Carbonic anhydrase 2</t>
+          <t>Catalase</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -498,32 +543,67 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>260</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1.11.1.6</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29246</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>4.2.1.1</t>
-        </is>
+        <v>527</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>59756</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>MSHHWGYGKHNGPEHWHKDFPIAKGERQSPVDIDTHTAKYDPSLKPLSVSYDQATSLRILNNGHAFNVEFDDSQDKAVLKGGPLDGTYRLIQFHFHWGSLDGQGSEHTVDKKKYAAELHLVHWNTKYGDFGKAVQQPDGLAVLGIFLKVGSAKPGLQKVVDVLDSIKTKGKSADFTNFDPRGLLPESLDYWTYPGSLTTPPLLECVTWIVLKEPISVSSEQVLKFRKLNFNGEGEPEELMVDNWRPAQPLKNRQIKASFK</t>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P04040 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (17 wpisów; metoda: krystalografia rentgenowska, mikroskopia elektronowa / cryo-EM); najlepsza rozdzielczość: 1.50 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 26, nici beta: 20, zakręty: 6.</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>MADSRDPASDQMQHWKEQRAAQKADVLTTGAGNPVGDKLNVITVGPRGPLLVQDVVFTDEMAHFDRERIPERVVHAKGAGAFGYFEVTHDITKYSKAKVFEHIGKKTPIAVRFSTVAGESGSADTVRDPRGFAVKFYTEDGNWDLVGNNTPIFFIRDPILFPSFIHSQKRNPQTHLKDPDMVWDFWSLRPESLHQVSFLFSDRGIPDGHRHMNGYGSHTFKLVNANGEAVYCKFHYKTDQGIKNLSVEDAARLSQEDPDYGIRDLFNAIATGKYPSWTFYIQVMTFNQAETFPFNPFDLTKVWPHKDYPLIPVGKLVLNRNPVNYFAEVEQIAFDPSNMPPGIEASPDKMLQGRLFAYPDTHRHRLGPNYLHIPVNCPYRARVANYQRDGPMCMQDNQGGAPNYYPNSFGAPEQQPSALEHSIQYSGEVRRFNTANDDNVTQVRAFYVNVLNEEQRKRLCENIAGHLKDAQIFIQKKAVKNFTEVHPDYGSHIQALLDKYNAEKPKNAIHTFVQSGSHLAAREKANL</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P04040</t>
+          <t>P04406</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Catalase</t>
+          <t>Glyceraldehyde-3-phosphate dehydrogenase</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -531,58 +611,1284 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>527</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1.12</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>59756</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1.11.1.6</t>
-        </is>
+        <v>335</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>36053</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>MADSRDPASDQMQHWKEQRAAQKADVLTTGAGNPVGDKLNVITVGPRGPLLVQDVVFTDEMAHFDRERIPERVVHAKGAGAFGYFEVTHDITKYSKAKVFEHIGKKTPIAVRFSTVAGESGSADTVRDPRGFAVKFYTEDGNWDLVGNNTPIFFIRDPILFPSFIHSQKRNPQTHLKDPDMVWDFWSLRPESLHQVSFLFSDRGIPDGHRHMNGYGSHTFKLVNANGEAVYCKFHYKTDQGIKNLSVEDAARLSQEDPDYGIRDLFNAIATGKYPSWTFYIQVMTFNQAETFPFNPFDLTKVWPHKDYPLIPVGKLVLNRNPVNYFAEVEQIAFDPSNMPPGIEASPDKMLQGRLFAYPDTHRHRLGPNYLHIPVNCPYRARVANYQRDGPMCMQDNQGGAPNYYPNSFGAPEQQPSALEHSIQYSGEVRRFNTANDDNVTQVRAFYVNVLNEEQRKRLCENIAGHLKDAQIFIQKKAVKNFTEVHPDYGSHIQALLDKYNAEKPKNAIHTFVQSGSHLAAREKANL</t>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P04406 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (21 wpisów; metoda: krystalografia rentgenowska, mikroskopia elektronowa / cryo-EM); najlepsza rozdzielczość: 1.52 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 14, nici beta: 20, zakręty: 5.</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>MGKVKVGVNGFGRIGRLVTRAAFNSGKVDIVAINDPFIDLNYMVYMFQYDSTHGKFHGTVKAENGKLVINGNPITIFQERDPSKIKWGDAGAEYVVESTGVFTTMEKAGAHLQGGAKRVIISAPSADAPMFVMGVNHEKYDNSLKIISNASCTTNCLAPLAKVIHDNFGIVEGLMTTVHAITATQKTVDGPSGKLWRDGRGALQNIIPASTGAAKAVGKVIPELNGKLTGMAFRVPTANVSVVDLTCRLEKPAKYDDIKKVVKQASEGPLKGILGYTEHQVVSSDFNSDTHSSTFDAGAGIALNDHFVKLISWYDNEFGYSNRVVDLMAHMASKE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>P00441</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Superoxide dismutase [Cu-Zn]</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1.15.1.1, 1.8.-.-</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>15936</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00441 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (153 wpisów; metoda: krystalografia rentgenowska, NMR, mikroskopia elektronowa / cryo-EM); najlepsza rozdzielczość: 0.98 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 5, nici beta: 22, zakręty: 2.</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>MATKAVCVLKGDGPVQGIINFEQKESNGPVKVWGSIKGLTEGLHGFHVHEFGDNTAGCTSAGPHFNPLSRKHGGPKDEERHVGDLGNVTADKDGVADVSIEDSVISLSGDHCIIGRTLVVHEKADDLGKGGNEESTKTGNAGSRLACGVIGIAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P00918</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Carbonic anhydrase 2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4.2.1.1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>29246</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00918 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (1182 wpisów; metoda: krystalografia rentgenowska, dyfrakcja neutronowa, inna metoda); najlepsza rozdzielczość: 0.90 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 12, nici beta: 23, zakręty: 5.</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>MSHHWGYGKHNGPEHWHKDFPIAKGERQSPVDIDTHTAKYDPSLKPLSVSYDQATSLRILNNGHAFNVEFDDSQDKAVLKGGPLDGTYRLIQFHFHWGSLDGQGSEHTVDKKKYAAELHLVHWNTKYGDFGKAVQQPDGLAVLGIFLKVGSAKPGLQKVVDVLDSIKTKGKSADFTNFDPRGLLPESLDYWTYPGSLTTPPLLECVTWIVLKEPISVSSEQVLKFRKLNFNGEGEPEELMVDNWRPAQPLKNRQIKASFK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>P00338</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>L-lactate dehydrogenase A chain</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1.1.1.27</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>332</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>36689</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1.1.1.27</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00338 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (46 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.55 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 18, nici beta: 14, zakręty: 1.</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>MATLKDQLIYNLLKEEQTPQNKITVVGVGAVGMACAISILMKDLADELALVDVIEDKLKGEMMDLQHGSLFLRTPKIVSGKDYNVTANSKLVIITAGARQQEGESRLNLVQRNVNIFKFIIPNVVKYSPNCKLLIVSNPVDILTYVAWKISGFPKNRVIGSGCNLDSARFRYLMGERLGVHPLSCHGWVLGEHGDSSVPVWSGMNVAGVSLKTLHPDLGTDKDKEQWKEVHKQVVESAYEVIKLKGYTSWAIGLSVADLAESIMKNLRRVHPVSTMIKGLYGIKDDVFLSVPCILGQNGISDLVKVTLTSEEEARLKKSADTLWGIQKELQF</t>
         </is>
       </c>
     </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P06733</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Alpha-enolase</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4.2.1.11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>434</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>47169</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P06733 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (8 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.33 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 25, nici beta: 11, zakręty: 4.</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>MSILKIHAREIFDSRGNPTVEVDLFTSKGLFRAAVPSGASTGIYEALELRDNDKTRYMGKGVSKAVEHINKTIAPALVSKKLNVTEQEKIDKLMIEMDGTENKSKFGANAILGVSLAVCKAGAVEKGVPLYRHIADLAGNSEVILPVPAFNVINGGSHAGNKLAMQEFMILPVGAANFREAMRIGAEVYHNLKNVIKEKYGKDATNVGDEGGFAPNILENKEGLELLKTAIGKAGYTDKVVIGMDVAASEFFRSGKYDLDFKSPDDPSRYISPDQLADLYKSFIKDYPVVSIEDPFDQDDWGAWQKFTASAGIQVVGDDLTVTNPKRIAKAVNEKSCNCLLLKVNQIGSVTESLQACKLAQANGWGVMVSHRSGETEDTFIADLVVGLCTGQIKTGAPCRSERLAKYNQLLRIEEELGSKAKFAGRNFRNPLAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P00558</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Phosphoglycerate kinase 1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2.7.11.1, 2.7.2.3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>44615</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00558 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (30 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.44 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 27, nici beta: 21, zakręty: 2.</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>MSLSNKLTLDKLDVKGKRVVMRVDFNVPMKNNQITNNQRIKAAVPSIKFCLDNGAKSVVLMSHLGRPDGVPMPDKYSLEPVAVELKSLLGKDVLFLKDCVGPEVEKACANPAAGSVILLENLRFHVEEEGKGKDASGNKVKAEPAKIEAFRASLSKLGDVYVNDAFGTAHRAHSSMVGVNLPQKAGGFLMKKELNYFAKALESPERPFLAILGGAKVADKIQLINNMLDKVNEMIIGGGMAFTFLKVLNNMEIGTSLFDEEGAKIVKDLMSKAEKNGVKITLPVDFVTADKFDENAKTGQATVASGIPAGWMGLDCGPESSKKYAEAVTRAKQIVWNGPVGVFEWEAFARGTKALMDEVVKATSRGCITIIGGGDTATCCAKWNTEDKVSHVSTGGGASLELLEGKVLPGVDALSNI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P11413</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Glucose-6-phosphate 1-dehydrogenase</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1.-.-.-, 1.1.1.49</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>515</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>59257</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P11413 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (25 wpisów; metoda: krystalografia rentgenowska, mikroskopia elektronowa / cryo-EM); najlepsza rozdzielczość: 1.89 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 34, nici beta: 22, zakręty: 8.</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>MAEQVALSRTQVCGILREELFQGDAFHQSDTHIFIIMGASGDLAKKKIYPTIWWLFRDGLLPENTFIVGYARSRLTVADIRKQSEPFFKATPEEKLKLEDFFARNSYVAGQYDDAASYQRLNSHMNALHLGSQANRLFYLALPPTVYEAVTKNIHESCMSQIGWNRIIVEKPFGRDLQSSDRLSNHISSLFREDQIYRIDHYLGKEMVQNLMVLRFANRIFGPIWNRDNIACVILTFKEPFGTEGRGGYFDEFGIIRDVMQNHLLQMLCLVAMEKPASTNSDDVRDEKVKVLKCISEVQANNVVLGQYVGNPDGEGEATKGYLDDPTVPRGSTTATFAAVVLYVENERWDGVPFILRCGKALNERKAEVRLQFHDVAGDIFHQQCKRNELVIRVQPNEAVYTKMMTKKPGMFFNPEESELDLTYGNRYKNVKLPDAYERLILDVFCGSQMHFVRSDELREAWRIFTPLLHQIELEKPKPIPYIYGSRGPTEADELMKRVGFQYEGTYKWVNPHKL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P35557</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hexokinase-4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2.7.1.1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>52191</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P35557 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (35 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.50 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 21, nici beta: 19, zakręty: 4.</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>MLDDRARMEAAKKEKVEQILAEFQLQEEDLKKVMRRMQKEMDRGLRLETHEEASVKMLPTYVRSTPEGSEVGDFLSLDLGGTNFRVMLVKVGEGEEGQWSVKTKHQMYSIPEDAMTGTAEMLFDYISECISDFLDKHQMKHKKLPLGFTFSFPVRHEDIDKGILLNWTKGFKASGAEGNNVVGLLRDAIKRRGDFEMDVVAMVNDTVATMISCYYEDHQCEVGMIVGTGCNACYMEEMQNVELVEGDEGRMCVNTEWGAFGDSGELDEFLLEYDRLVDESSANPGQQLYEKLIGGKYMGELVRLVLLRLVDENLLFHGEASEQLRTRGAFETRFVSQVESDTGDRKQIYNILSTLGLRPSTTDCDIVRRACESVSTRAAHMCSAGLAGVINRMRESRSEDVMRITVGVDGSVYKLHPSFKERFHASVRRLTPSCEITFIESEEGSGRGAALVSAVACKKACMLGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>P08246</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Neutrophil elastase</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3.4.21.37</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>28518</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P08246 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (38 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.14 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 7, nici beta: 18, zakręty: 2.</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>MTLGRRLACLFLACVLPALLLGGTALASEIVGGRRARPHAWPFMVSLQLRGGHFCGATLIAPNFVMSAAHCVANVNVRAVRVVLGAHNLSRREPTRQVFAVQRIFENGYDPVNLLNDIVILQLNGSATINANVQVAQLPAQGRRLGNGVQCLAMGWGLLGRNRGIASVLQELNVTVVTSLCRRSNVCTLVRGRQAGVCFGDSGSPLVCNGLIHGIASFVRGGCASGLYPDAFAPVAQFVNWIDSIIQRSEDNPCPHPRDPDPASRTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>P00709</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Alpha-lactalbumin</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Brak</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>16225</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00709 jest rekordem reviewed/Swiss-Prot, nie posiada numeru EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (7 wpisów; metoda: krystalografia rentgenowska, NMR); najlepsza rozdzielczość: 1.15 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 9, nici beta: 4, zakręty: 3.</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>MRFFVPLFLVGILFPAILAKQFTKCELSQLLKDIDGYGGIALPELICTMFHTSGYDTQAIVENNESTEYGLFQISNKLWCKSSQVPQSRNICDISCDKFLDDDITDDIMCAKKILDIKGIDYWLAHKALCTEKLEQWLCEKL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>P00734</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Prothrombin</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3.4.21.5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>70037</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P00734 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (472 wpisów; metoda: krystalografia rentgenowska, inna metoda, NMR); najlepsza rozdzielczość: 1.12 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 24, nici beta: 40, zakręty: 13.</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>MAHVRGLQLPGCLALAALCSLVHSQHVFLAPQQARSLLQRVRRANTFLEEVRKGNLERECVEETCSYEEAFEALESSTATDVFWAKYTACETARTPRDKLAACLEGNCAEGLGTNYRGHVNITRSGIECQLWRSRYPHKPEINSTTHPGADLQENFCRNPDSSTTGPWCYTTDPTVRRQECSIPVCGQDQVTVAMTPRSEGSSVNLSPPLEQCVPDRGQQYQGRLAVTTHGLPCLAWASAQAKALSKHQDFNSAVQLVENFCRNPDGDEEGVWCYVAGKPGDFGYCDLNYCEEAVEEETGDGLDEDSDRAIEGRTATSEYQTFFNPRTFGSGEADCGLRPLFEKKSLEDKTERELLESYIDGRIVEGSDAEIGMSPWQVMLFRKSPQELLCGASLISDRWVLTAAHCLLYPPWDKNFTENDLLVRIGKHSRTRYERNIEKISMLEKIYIHPRYNWRENLDRDIALMKLKKPVAFSDYIHPVCLPDRETAASLLQAGYKGRVTGWGNLKETWTANVGKGQPSVLQVVNLPIVERPVCKDSTRIRITDNMFCAGYKPDEGKRGDACEGDSGGPFVMKSPFNNRWYQMGIVSWGEGCDRDGKYGFYTHVFRLKKWIQKVIDQFGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>P08254</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Stromelysin-1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3.4.24.17</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>477</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>53977</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P08254 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (44 wpisów; metoda: krystalografia rentgenowska, NMR); najlepsza rozdzielczość: 1.50 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 9, nici beta: 17, zakręty: 1.</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>MKSLPILLLLCVAVCSAYPLDGAARGEDTSMNLVQKYLENYYDLKKDVKQFVRRKDSGPVVKKIREMQKFLGLEVTGKLDSDTLEVMRKPRCGVPDVGHFRTFPGIPKWRKTHLTYRIVNYTPDLPKDAVDSAVEKALKVWEEVTPLTFSRLYEGEADIMISFAVREHGDFYPFDGPGNVLAHAYAPGPGINGDAHFDDDEQWTKDTTGTNLFLVAAHEIGHSLGLFHSANTEALMYPLYHSLTDLTRFRLSQDDINGIQSLYGPPPDSPETPLVPTEPVPPEPGTPANCDPALSFDAVSTLRGEILIFKDRHFWRKSLRKLEPELHLISSFWPSLPSGVDAAYEVTSKDLVFIFKGNQFWAIRGNEVRAGYPRGIHTLGFPPTVRKIDAAISDKEKNKTYFFVEDKYWRFDEKRNSMEPGFPKQIAEDFPGIDSKIDAVFEEFGFFYFFTGSSQLEFDPNAKKVTHTLKSNSWLNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>P05164</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Myeloperoxidase</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1.11.2.2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>83869</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P05164 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (49 wpisów; metoda: krystalografia rentgenowska, mikroskopia elektronowa / cryo-EM); najlepsza rozdzielczość: 1.20 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 38, nici beta: 21, zakręty: 11.</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>MGVPFFSSLRCMVDLGPCWAGGLTAEMKLLLALAGLLAILATPQPSEGAAPAVLGEVDTSLVLSSMEEAKQLVDKAYKERRESIKQRLRSGSASPMELLSYFKQPVAATRTAVRAADYLHVALDLLERKLRSLWRRPFNVTDVLTPAQLNVLSKSSGCAYQDVGVTCPEQDKYRTITGMCNNRRSPTLGASNRAFVRWLPAEYEDGFSLPYGWTPGVKRNGFPVALARAVSNEIVRFPTDQLTPDQERSLMFMQWGQLLDHDLDFTPEPAARASFVTGVNCETSCVQQPPCFPLKIPPNDPRIKNQADCIPFFRSCPACPGSNITIRNQINALTSFVDASMVYGSEEPLARNLRNMSNQLGLLAVNQRFQDNGRALLPFDNLHDDPCLLTNRSARIPCFLAGDTRSSEMPELTSMHTLLLREHNRLATELKSLNPRWDGERLYQEARKIVGAMVQIITYRDYLPLVLGPTAMRKYLPTYRSYNDSVDPRIANVFTNAFRYGHTLIQPFMFRLDNRYQPMEPNPRVPLSRVFFASWRVVLEGGIDPILRGLMATPAKLNRQNQIAVDEIRERLFEQVMRIGLDLPALNMQRSRDHGLPGYNAWRRFCGLPQPETVGQLGTVLRNLKLARKLMEQYGTPNNIDIWMGGVSEPLKRKGRVGPLLACIIGTQFRKLRDGDRFWWENEGVFSMQQRQALAQISLPRIICDNTGITTVSKNNIFMSNSYPRDFVNCSTLPALNLASWREAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>P05181</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Cytochrome P450 2E1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1.14.14.1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>56849</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P05181 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (6 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 2.20 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 26, nici beta: 15, zakręty: 6.</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>MSALGVTVALLVWAAFLLLVSMWRQVHSSWNLPPGPFPLPIIGNLFQLELKNIPKSFTRLAQRFGPVFTLYVGSQRMVVMHGYKAVKEALLDYKDEFSGRGDLPAFHAHRDRGIIFNNGPTWKDIRRFSLTTLRNYGMGKQGNESRIQREAHFLLEALRKTQGQPFDPTFLIGCAPCNVIADILFRKHFDYNDEKFLRLMYLFNENFHLLSTPWLQLYNNFPSFLHYLPGSHRKVIKNVAEVKEYVSERVKEHHQSLDPNCPRDLTDCLLVEMEKEKHSAERLYTMDGITVTVADLFFAGTETTSTTLRYGLLILMKYPEIEEKLHEEIDRVIGPSRIPAIKDRQEMPYMDAVVHEIQRFITLVPSNLPHEATRDTIFRGYLIPKGTVVVPTLDSVLYDNQEFPDPEKFKPEHFLNENGKFKYSDYFKPFSTGKRVCAGEGLARMELFLLLCAILQHFNLKPLVDPKDIDLSPIHIGFGCIPPRYKLCVIPRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>P08684</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Cytochrome P450 3A4</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1.14.14.1</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>57343</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P08684 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (119 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.70 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 34, nici beta: 17, zakręty: 9.</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>MALIPDLAMETWLLLAVSLVLLYLYGTHSHGLFKKLGIPGPTPLPFLGNILSYHKGFCMFDMECHKKYGKVWGFYDGQQPVLAITDPDMIKTVLVKECYSVFTNRRPFGPVGFMKSAISIAEDEEWKRLRSLLSPTFTSGKLKEMVPIIAQYGDVLVRNLRREAETGKPVTLKDVFGAYSMDVITSTSFGVNIDSLNNPQDPFVENTKKLLRFDFLDPFFLSITVFPFLIPILEVLNICVFPREVTNFLRKSVKRMKESRLEDTQKHRVDFLQLMIDSQNSKETESHKALSDLELVAQSIIFIFAGYETTSSVLSFIMYELATHPDVQQKLQEEIDAVLPNKAPPTYDTVLQMEYLDMVVNETLRLFPIAMRLERVCKKDVEINGMFIPKGVVVMIPSYALHRDPKYWTEPEKFLPERFSKKNKDNIDPYIYTPFGSGPRNCIGMRFALMNMKLALIRVLQNFSFKPCKETQIPLKLSLGGLLQPEKPVVLKVESRDGTVSGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>P09917</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Polyunsaturated fatty acid 5-lipoxygenase</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1.13.11.-</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>77983</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P09917 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (9 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.98 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 44, nici beta: 22, zakręty: 5.</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>MPSYTVTVATGSQWFAGTDDYIYLSLVGSAGCSEKHLLDKPFYNDFERGAVDSYDVTVDEELGEIQLVRIEKRKYWLNDDWYLKYITLKTPHGDYIEFPCYRWITGDVEVVLRDGRAKLARDDQIHILKQHRRKELETRQKQYRWMEWNPGFPLSIDAKCHKDLPRDIQFDSEKGVDFVLNYSKAMENLFINRFMHMFQSSWNDFADFEKIFVKISNTISERVMNHWQEDLMFGYQFLNGCNPVLIRRCTELPEKLPVTTEMVECSLERQLSLEQEVQQGNIFIVDFELLDGIDANKTDPCTLQFLAAPICLLYKNLANKIVPIAIQLNQIPGDENPIFLPSDAKYDWLLAKIWVRSSDFHVHQTITHLLRTHLVSEVFGIAMYRQLPAVHPIFKLLVAHVRFTIAINTKAREQLICECGLFDKANATGGGGHVQMVQRAMKDLTYASLCFPEAIKARGMESKEDIPYYFYRDDGLLVWEAIRTFTAEVVDIYYEGDQVVEEDPELQDFVNDVYVYGMRGRKSSGFPKSVKSREQLSEYLTVVIFTASAQHAAVNFGQYDWCSWIPNAPPTMRAPPPTAKGVVTIEQIVDTLPDRGRSCWHLGAVWALSQFQENELFLGMYPEEHFIEKPVKEAMARFRKNLEAIVSVIAERNKKKQLPYYYLSPDRIPNSVAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>P29474</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Nitric oxide synthase 3</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1.14.13.39</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>133275</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P29474 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (90 wpisów; metoda: krystalografia rentgenowska, NMR); najlepsza rozdzielczość: 1.73 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 27, nici beta: 23, zakręty: 2.</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>MGNLKSVAQEPGPPCGLGLGLGLGLCGKQGPATPAPEPSRAPASLLPPAPEHSPPSSPLTQPPEGPKFPRVKNWEVGSITYDTLSAQAQQDGPCTPRRCLGSLVFPRKLQGRPSPGPPAPEQLLSQARDFINQYYSSIKRSGSQAHEQRLQEVEAEVAATGTYQLRESELVFGAKQAWRNAPRCVGRIQWGKLQVFDARDCRSAQEMFTYICNHIKYATNRGNLRSAITVFPQRCPGRGDFRIWNSQLVRYAGYRQQDGSVRGDPANVEITELCIQHGWTPGNGRFDVLPLLLQAPDDPPELFLLPPELVLEVPLEHPTLEWFAALGLRWYALPAVSNMLLEIGGLEFPAAPFSGWYMSTEIGTRNLCDPHRYNILEDVAVCMDLDTRTTSSLWKDKAAVEINVAVLHSYQLAKVTIVDHHAATASFMKHLENEQKARGGCPADWAWIVPPISGSLTPVFHQEMVNYFLSPAFRYQPDPWKGSAAKGTGITRKKTFKEVANAVKISASLMGTVMAKRVKATILYGSETGRAQSYAQQLGRLFRKAFDPRVLCMDEYDVVSLEHETLVLVVTSTFGNGDPPENGESFAAALMEMSGPYNSSPRPEQHKSYKIRFNSISCSDPLVSSWRRKRKESSNTDSAGALGTLRFCVFGLGSRAYPHFCAFARAVDTRLEELGGERLLQLGQGDELCGQEEAFRGWAQAAFQAACETFCVGEDAKAAARDIFSPKRSWKRQRYRLSAQAEGLQLLPGLIHVHRRKMFQATIRSVENLQSSKSTRATILVRLDTGGQEGLQYQPGDHIGVCPPNRPGLVEALLSRVEDPPAPTEPVAVEQLEKGSPGGPPPGWVRDPRLPPCTLRQALTFFLDITSPPSPQLLRLLSTLAEEPREQQELEALSQDPRRYEEWKWFRCPTLLEVLEQFPSVALPAPLLLTQLPLLQPRYYSVSSAPSTHPGEIHLTVAVLAYRTQDGLGPLHYGVCSTWLSQLKPGDPVPCFIRGAPSFRLPPDPSLPCILVGPGTGIAPFRGFWQERLHDIESKGLQPTPMTLVFGCRCSQLDHLYRDEVQNAQQRGVFGRVLTAFSREPDNPKTYVQDILRTELAAEVHRVLCLERGHMFVCGDVTMATNVLQTVQRILATEGDMELDEAGDVIGVLRDQQRYHEDIFGLTLRTQEVTSRIRTQSFSLQERQLRGAVPWAFDPPGSDTNSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>P15121</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Aldo-keto reductase family 1 member B1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1.1.1.21, 1.1.1.300, 1.1.1.372, 1.1.1.54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>35853</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P15121 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (177 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 0.66 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 15, nici beta: 15, zakręty: 2.</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>MASRLLLNNGAKMPILGLGTWKSPPGQVTEAVKVAIDVGYRHIDCAHVYQNENEVGVAIQEKLREQVVKREELFIVSKLWCTYHEKGLVKGACQKTLSDLKLDYLDLYLIHWPTGFKPGKEFFPLDESGNVVPSDTNILDTWAAMEELVDEGLVKAIGISNFNHLQVEMILNKPGLKYKPAVNQIECHPYLTQEKLIQYCQSKGIVVTAYSPLGSPDRPWAKPEDPSLLEDPRIKAIAAKHNKTTAQVLIRFPMQRNLVVIPKSVTPERIAENFKVFDFELSSQDMTTLLSYNRNWRVCALLSCTSHKDYPFHEEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>P04075</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Fructose-bisphosphate aldolase A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4.1.2.13</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>39420</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unikalna</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Tak</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Rekord P04075 jest rekordem reviewed/Swiss-Prot, posiada numer EC i posiada sekwencję aminokwasową. Struktura: struktura 3D eksperymentalna w PDB (8 wpisów; metoda: krystalografia rentgenowska); najlepsza rozdzielczość: 1.88 Å; model 3D predykcyjny AlphaFold; struktura drugorzędowa/2D: helisy: 19, nici beta: 12, zakręty: 3.</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>MPYQYPALTPEQKKELSDIAHRIVAPGKGILAADESTGSIAKRLQSIGTENTEENRRFYRQLLLTADDRVNPCIGGVILFHETLYQKADDGRPFPQVIKSKGGVVGIKVDKGVVPLAGTNGETTTQGLDGLSERCAQYKKDGADFAKWRCVLKIGEHTPSALAIMENANVLARYASICQQNGIVPIVEPEILPDGDHDLKRCQYVTEKVLAAVYKALSDHHIYLEGTLLKPNMVTPGHACTQKFSHEEIAMATVTALRRTVPPAVTGITFLSGGQSEEEASINLNAINKCPLLKPWALTFSYGRALQASALKAWGGKKENLKAAQEEYVKRALANSLACQGKYTPSGQAGAAASESLFVSNHAY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:P21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>